--- a/data/trans_dic/P57_AF_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,56; 63,66</t>
+          <t>54,6; 63,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,35; 63,05</t>
+          <t>53,34; 62,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,28; 72,74</t>
+          <t>62,83; 73,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,59; 55,68</t>
+          <t>47,18; 56,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,45; 58,92</t>
+          <t>47,52; 59,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,89; 66,76</t>
+          <t>55,1; 66,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,96; 76,01</t>
+          <t>65,74; 75,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,3; 49,66</t>
+          <t>40,95; 48,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,19; 60,36</t>
+          <t>53,4; 60,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,88; 63,63</t>
+          <t>55,96; 63,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,84; 72,71</t>
+          <t>66,01; 72,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,22; 51,5</t>
+          <t>45,65; 51,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,72; 58,56</t>
+          <t>48,23; 59,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,57; 65,81</t>
+          <t>55,64; 65,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,55; 74,52</t>
+          <t>64,47; 74,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,05; 60,97</t>
+          <t>51,11; 60,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,34; 64,3</t>
+          <t>54,43; 63,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,01; 71,53</t>
+          <t>60,62; 71,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,16; 75,21</t>
+          <t>65,71; 75,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,49; 60,53</t>
+          <t>52,03; 60,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,81; 60,09</t>
+          <t>52,51; 59,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59,81; 66,92</t>
+          <t>59,52; 66,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,03; 73,11</t>
+          <t>66,38; 73,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,86; 59,45</t>
+          <t>52,26; 59,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,19; 69,63</t>
+          <t>61,53; 69,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,31; 65,2</t>
+          <t>57,27; 65,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,65; 80,09</t>
+          <t>72,69; 79,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,75; 59,4</t>
+          <t>14,41; 59,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,89; 70,93</t>
+          <t>56,19; 70,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,62; 70,33</t>
+          <t>58,43; 70,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,79; 83,63</t>
+          <t>71,03; 83,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,33; 63,72</t>
+          <t>50,62; 63,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,58; 68,63</t>
+          <t>61,82; 68,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,08; 65,65</t>
+          <t>59,18; 65,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,66; 79,92</t>
+          <t>73,14; 79,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 58,79</t>
+          <t>16,55; 59,23</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,88; 66,57</t>
+          <t>60,97; 66,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,42; 67,06</t>
+          <t>61,09; 67,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 77,62</t>
+          <t>72,57; 77,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,68; 62,92</t>
+          <t>55,38; 62,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,74; 68,65</t>
+          <t>61,25; 68,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,97; 74,05</t>
+          <t>67,1; 73,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,51; 77,68</t>
+          <t>72,07; 77,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55,53; 82,28</t>
+          <t>55,5; 82,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,08; 66,44</t>
+          <t>62,31; 66,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64,52; 68,82</t>
+          <t>64,81; 69,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,97; 77,09</t>
+          <t>72,96; 76,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,32; 73,95</t>
+          <t>57,29; 75,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,38; 67,6</t>
+          <t>57,61; 67,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,16; 71,33</t>
+          <t>63,11; 71,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,13; 81,18</t>
+          <t>74,15; 81,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,5; 67,45</t>
+          <t>57,64; 67,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,36; 70,55</t>
+          <t>62,33; 70,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,17; 73,7</t>
+          <t>67,02; 73,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,93; 83,9</t>
+          <t>78,21; 83,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,96; 64,32</t>
+          <t>44,46; 64,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,49; 68,27</t>
+          <t>61,65; 68,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66,55; 71,91</t>
+          <t>66,47; 71,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,27; 81,42</t>
+          <t>77,31; 81,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,2; 64,26</t>
+          <t>47,66; 64,16</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42,15; 53,12</t>
+          <t>42,01; 53,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,52; 57,63</t>
+          <t>45,55; 57,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,25; 75,37</t>
+          <t>64,23; 74,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,47; 47,36</t>
+          <t>25,91; 45,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,79; 61,28</t>
+          <t>55,68; 61,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,62; 66,5</t>
+          <t>60,86; 66,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,14; 79,44</t>
+          <t>74,11; 79,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,39; 62,51</t>
+          <t>55,71; 62,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54,03; 59,23</t>
+          <t>53,99; 59,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58,65; 64,04</t>
+          <t>58,7; 64,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,13; 77,81</t>
+          <t>73,03; 77,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,66; 57,09</t>
+          <t>49,84; 57,24</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,84; 62,41</t>
+          <t>58,97; 62,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,27; 63,67</t>
+          <t>60,27; 63,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,3; 75,43</t>
+          <t>72,4; 75,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,18; 56,63</t>
+          <t>38,58; 56,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,57; 62,91</t>
+          <t>59,63; 62,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,2; 68,4</t>
+          <t>65,16; 68,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,47; 77,45</t>
+          <t>74,72; 77,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,71; 65,67</t>
+          <t>54,13; 65,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59,74; 62,08</t>
+          <t>59,78; 62,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63,28; 65,61</t>
+          <t>63,19; 65,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73,82; 75,97</t>
+          <t>73,89; 76,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,26; 58,93</t>
+          <t>49,51; 59,18</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>256940; 299785</t>
+          <t>257151; 300422</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>232239; 274462</t>
+          <t>232180; 274155</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>270981; 311501</t>
+          <t>269045; 312875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233675; 279261</t>
+          <t>236620; 281270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145526; 180684</t>
+          <t>145745; 181140</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>171393; 208461</t>
+          <t>172043; 208374</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>225894; 260325</t>
+          <t>225157; 259326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>184238; 221538</t>
+          <t>182668; 218491</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>413586; 469361</t>
+          <t>415273; 471572</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>417691; 475615</t>
+          <t>418291; 472809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>507456; 560405</t>
+          <t>508724; 560749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>428537; 487982</t>
+          <t>432574; 490989</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>178772; 214891</t>
+          <t>176973; 216651</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>231351; 273989</t>
+          <t>231650; 272461</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>242595; 280087</t>
+          <t>242303; 280594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228934; 273373</t>
+          <t>229203; 273005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>202076; 239113</t>
+          <t>202392; 237872</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>201170; 239794</t>
+          <t>203226; 240195</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>239560; 276494</t>
+          <t>241561; 276379</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>194850; 229072</t>
+          <t>196901; 229292</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>390129; 443966</t>
+          <t>387908; 442461</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>449503; 502926</t>
+          <t>447311; 501567</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>490934; 543522</t>
+          <t>493479; 545048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>437062; 491540</t>
+          <t>432148; 489382</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>331354; 377100</t>
+          <t>333194; 376475</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>359667; 409208</t>
+          <t>359416; 408169</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>379160; 417999</t>
+          <t>379372; 417092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84760; 394938</t>
+          <t>95780; 396762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94889; 118312</t>
+          <t>93733; 117978</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>151946; 182300</t>
+          <t>151440; 182551</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>116497; 137629</t>
+          <t>116893; 137829</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84773; 105242</t>
+          <t>83613; 104615</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>436187; 486105</t>
+          <t>437916; 486150</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>523894; 582185</t>
+          <t>524775; 582688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>505700; 548626</t>
+          <t>502069; 549151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>138452; 487992</t>
+          <t>137392; 491599</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>753934; 824380</t>
+          <t>754995; 825552</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>705835; 770754</t>
+          <t>702047; 771802</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>825533; 884592</t>
+          <t>827103; 885667</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>572695; 647152</t>
+          <t>569580; 644169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>441008; 490337</t>
+          <t>437494; 489493</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>510757; 564728</t>
+          <t>511748; 563943</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>588489; 639294</t>
+          <t>593109; 641199</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>540071; 800186</t>
+          <t>539727; 799006</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1212240; 1297371</t>
+          <t>1216644; 1297770</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1233545; 1315823</t>
+          <t>1239165; 1319265</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1432118; 1513041</t>
+          <t>1431941; 1509039</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1146915; 1479720</t>
+          <t>1146312; 1514563</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>201165; 236984</t>
+          <t>201950; 238221</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>319282; 360586</t>
+          <t>319004; 361681</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458510; 502110</t>
+          <t>458617; 501419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>269501; 316180</t>
+          <t>270178; 317655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>354047; 400529</t>
+          <t>353898; 399538</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>506697; 555962</t>
+          <t>505585; 555287</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>573925; 617876</t>
+          <t>575952; 616623</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>348438; 534053</t>
+          <t>369150; 534260</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>564658; 626971</t>
+          <t>566125; 626246</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838371; 905981</t>
+          <t>837453; 905646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1047025; 1103151</t>
+          <t>1047497; 1107490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>639121; 834831</t>
+          <t>619199; 833502</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>125335; 157964</t>
+          <t>124933; 159994</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>121486; 153815</t>
+          <t>121556; 154217</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>183872; 215703</t>
+          <t>183831; 213638</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62970; 112644</t>
+          <t>61628; 108609</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>696685; 765297</t>
+          <t>695342; 765338</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>666937; 731585</t>
+          <t>669499; 734808</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>799879; 857065</t>
+          <t>799507; 854242</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>417812; 471515</t>
+          <t>420233; 472310</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>835334; 915814</t>
+          <t>834776; 915559</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>801749; 875370</t>
+          <t>802460; 880998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>998220; 1062185</t>
+          <t>996927; 1063644</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>492704; 566471</t>
+          <t>494495; 567931</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1921402; 2038030</t>
+          <t>1925725; 2037241</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2049609; 2165423</t>
+          <t>2049666; 2166906</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2436828; 2542200</t>
+          <t>2440069; 2541315</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1345864; 1897182</t>
+          <t>1292323; 1898230</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2011246; 2123935</t>
+          <t>2013143; 2123655</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2297367; 2410219</t>
+          <t>2296250; 2412891</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2615951; 2720701</t>
+          <t>2624727; 2716016</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1940549; 2329157</t>
+          <t>1919948; 2320172</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3968041; 4123320</t>
+          <t>3970723; 4129172</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4381608; 4543612</t>
+          <t>4375691; 4541168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5080954; 5229606</t>
+          <t>5086372; 5235407</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3397061; 4064034</t>
+          <t>3414697; 4081664</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AF_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,6; 63,79</t>
+          <t>53,65; 63,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,34; 62,98</t>
+          <t>53,34; 63,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,83; 73,06</t>
+          <t>63,18; 72,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,18; 56,08</t>
+          <t>47,64; 55,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,52; 59,06</t>
+          <t>47,43; 58,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,1; 66,73</t>
+          <t>54,6; 66,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,74; 75,72</t>
+          <t>65,71; 75,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,95; 48,98</t>
+          <t>41,64; 49,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,4; 60,64</t>
+          <t>53,51; 60,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,96; 63,25</t>
+          <t>55,93; 63,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,01; 72,76</t>
+          <t>65,82; 73,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,65; 51,81</t>
+          <t>46,3; 52,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,23; 59,04</t>
+          <t>48,43; 58,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,64; 65,45</t>
+          <t>55,83; 65,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,47; 74,66</t>
+          <t>64,76; 74,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,11; 60,88</t>
+          <t>52,87; 62,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,43; 63,97</t>
+          <t>54,45; 64,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,62; 71,65</t>
+          <t>60,9; 71,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,71; 75,18</t>
+          <t>64,91; 75,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,03; 60,59</t>
+          <t>51,57; 59,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,51; 59,89</t>
+          <t>52,8; 60,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59,52; 66,74</t>
+          <t>59,02; 66,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,38; 73,31</t>
+          <t>66,47; 73,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,26; 59,19</t>
+          <t>53,63; 60,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,53; 69,52</t>
+          <t>61,24; 69,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,27; 65,03</t>
+          <t>57,02; 65,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,69; 79,92</t>
+          <t>72,44; 80,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 59,68</t>
+          <t>52,77; 62,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,19; 70,73</t>
+          <t>56,59; 71,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,43; 70,43</t>
+          <t>58,61; 71,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,03; 83,75</t>
+          <t>70,93; 84,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,62; 63,34</t>
+          <t>50,19; 62,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,82; 68,63</t>
+          <t>61,5; 68,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,18; 65,71</t>
+          <t>58,73; 65,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,14; 79,99</t>
+          <t>73,14; 79,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 59,23</t>
+          <t>53,29; 60,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,97; 66,67</t>
+          <t>60,96; 66,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,09; 67,16</t>
+          <t>61,17; 67,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,57; 77,71</t>
+          <t>72,83; 77,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,38; 62,63</t>
+          <t>55,75; 62,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,25; 68,53</t>
+          <t>61,31; 68,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,1; 73,94</t>
+          <t>67,09; 73,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,07; 77,91</t>
+          <t>71,79; 77,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55,5; 82,16</t>
+          <t>54,83; 60,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,31; 66,46</t>
+          <t>62,17; 66,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64,81; 69,0</t>
+          <t>64,56; 68,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,96; 76,89</t>
+          <t>72,77; 77,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,29; 75,69</t>
+          <t>56,2; 60,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,61; 67,96</t>
+          <t>57,08; 67,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,11; 71,55</t>
+          <t>62,75; 71,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,15; 81,07</t>
+          <t>74,24; 81,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,64; 67,77</t>
+          <t>59,87; 69,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,33; 70,37</t>
+          <t>62,33; 70,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,02; 73,61</t>
+          <t>67,02; 73,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,21; 83,73</t>
+          <t>77,77; 83,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,46; 64,34</t>
+          <t>63,07; 68,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,65; 68,2</t>
+          <t>61,89; 68,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66,47; 71,89</t>
+          <t>66,65; 71,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,31; 81,74</t>
+          <t>77,16; 81,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,66; 64,16</t>
+          <t>62,77; 67,72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42,01; 53,8</t>
+          <t>42,07; 52,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,55; 57,78</t>
+          <t>46,26; 58,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,23; 74,65</t>
+          <t>64,78; 75,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,91; 45,66</t>
+          <t>28,96; 49,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,68; 61,29</t>
+          <t>56,07; 61,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,86; 66,79</t>
+          <t>60,46; 66,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,11; 79,18</t>
+          <t>74,48; 79,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,71; 62,61</t>
+          <t>56,54; 63,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,99; 59,22</t>
+          <t>54,17; 59,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58,7; 64,45</t>
+          <t>58,76; 64,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,03; 77,92</t>
+          <t>72,99; 77,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49,84; 57,24</t>
+          <t>51,63; 58,82</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,97; 62,38</t>
+          <t>58,85; 62,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60,27; 63,72</t>
+          <t>60,28; 63,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,4; 75,4</t>
+          <t>72,59; 75,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,58; 56,66</t>
+          <t>54,97; 58,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,63; 62,9</t>
+          <t>59,56; 62,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,16; 68,47</t>
+          <t>65,26; 68,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,72; 77,31</t>
+          <t>74,48; 77,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,13; 65,41</t>
+          <t>56,81; 59,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59,78; 62,17</t>
+          <t>59,8; 62,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63,19; 65,58</t>
+          <t>63,28; 65,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73,89; 76,06</t>
+          <t>73,9; 76,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,51; 59,18</t>
+          <t>56,53; 58,86</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257985</t>
+          <t>284315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>200993</t>
+          <t>222914</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>458979</t>
+          <t>507230</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>257151; 300422</t>
+          <t>252642; 299427</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>232180; 274155</t>
+          <t>232189; 276799</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269045; 312875</t>
+          <t>270565; 311947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236620; 281270</t>
+          <t>260525; 306015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145745; 181140</t>
+          <t>145467; 180401</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>172043; 208374</t>
+          <t>170498; 208470</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>225157; 259326</t>
+          <t>225041; 259196</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>182668; 218491</t>
+          <t>202778; 241016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>415273; 471572</t>
+          <t>416083; 472167</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>418291; 472809</t>
+          <t>418078; 475877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>508724; 560749</t>
+          <t>507299; 563743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>432574; 490989</t>
+          <t>478702; 539548</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250650</t>
+          <t>276069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>212807</t>
+          <t>234634</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>463458</t>
+          <t>510703</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>176973; 216651</t>
+          <t>177697; 215311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>231650; 272461</t>
+          <t>232440; 273658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>242303; 280594</t>
+          <t>243405; 279214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>229203; 273005</t>
+          <t>253416; 298763</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>202392; 237872</t>
+          <t>202466; 239030</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>203226; 240195</t>
+          <t>204155; 240891</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>241561; 276379</t>
+          <t>238627; 275770</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>196901; 229292</t>
+          <t>216042; 251092</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>387908; 442461</t>
+          <t>390101; 443499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447311; 501567</t>
+          <t>443544; 502531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>493479; 545048</t>
+          <t>494202; 545594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>432148; 489382</t>
+          <t>481735; 540525</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243607</t>
+          <t>269685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94639</t>
+          <t>105038</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>338246</t>
+          <t>374723</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>333194; 376475</t>
+          <t>331663; 377999</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>359416; 408169</t>
+          <t>357864; 408136</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>379372; 417092</t>
+          <t>378080; 417740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95780; 396762</t>
+          <t>247136; 292572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93733; 117978</t>
+          <t>94391; 119040</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>151440; 182551</t>
+          <t>151912; 184364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>116893; 137829</t>
+          <t>116734; 138381</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83613; 104615</t>
+          <t>93163; 115780</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>437916; 486150</t>
+          <t>435663; 485553</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>524775; 582688</t>
+          <t>520827; 581148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>502069; 549151</t>
+          <t>502134; 546538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>137392; 491599</t>
+          <t>348450; 398358</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609007</t>
+          <t>666734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>638655</t>
+          <t>493626</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1247663</t>
+          <t>1160359</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>754995; 825552</t>
+          <t>754881; 824534</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>702047; 771802</t>
+          <t>703024; 771107</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>827103; 885667</t>
+          <t>830069; 888114</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>569580; 644169</t>
+          <t>627467; 702551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>437494; 489493</t>
+          <t>437908; 490596</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>511748; 563943</t>
+          <t>511706; 563311</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>593109; 641199</t>
+          <t>590804; 640864</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>539727; 799006</t>
+          <t>468333; 518549</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1216644; 1297770</t>
+          <t>1213911; 1297157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1239165; 1319265</t>
+          <t>1234396; 1317103</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1431941; 1509039</t>
+          <t>1428197; 1511711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1146312; 1514563</t>
+          <t>1112577; 1202705</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294645</t>
+          <t>361065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>473543</t>
+          <t>538941</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>768188</t>
+          <t>900006</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>201950; 238221</t>
+          <t>200093; 237227</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>319004; 361681</t>
+          <t>317216; 360845</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458617; 501419</t>
+          <t>459218; 500983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>270178; 317655</t>
+          <t>335251; 386397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>353898; 399538</t>
+          <t>353883; 401324</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>505585; 555287</t>
+          <t>505572; 555506</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>575952; 616623</t>
+          <t>572730; 618000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>369150; 534260</t>
+          <t>516322; 561262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>566125; 626246</t>
+          <t>568383; 624631</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837453; 905646</t>
+          <t>839694; 905632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1047497; 1107490</t>
+          <t>1045457; 1108715</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>619199; 833502</t>
+          <t>865396; 933601</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84695</t>
+          <t>91298</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>501275</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>531468</t>
+          <t>592573</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>124933; 159994</t>
+          <t>125105; 157379</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>121556; 154217</t>
+          <t>123469; 155670</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>183831; 213638</t>
+          <t>185394; 216017</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61628; 108609</t>
+          <t>67921; 115098</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>695342; 765338</t>
+          <t>700228; 768024</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>669499; 734808</t>
+          <t>665096; 731951</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>799507; 854242</t>
+          <t>803537; 855387</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>420233; 472310</t>
+          <t>473143; 530456</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>834776; 915559</t>
+          <t>837549; 912919</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>802460; 880998</t>
+          <t>803286; 876782</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>996927; 1063644</t>
+          <t>996417; 1061479</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>494495; 567931</t>
+          <t>553214; 630183</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1740590</t>
+          <t>1949166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2067411</t>
+          <t>2096429</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3808001</t>
+          <t>4045595</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1925725; 2037241</t>
+          <t>1921793; 2035721</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2049666; 2166906</t>
+          <t>2050218; 2166945</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2440069; 2541315</t>
+          <t>2446681; 2551547</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1292323; 1898230</t>
+          <t>1876977; 2005709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2013143; 2123655</t>
+          <t>2010867; 2124756</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2296250; 2412891</t>
+          <t>2299511; 2407066</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2624727; 2716016</t>
+          <t>2616542; 2721594</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1919948; 2320172</t>
+          <t>2045847; 2151093</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3970723; 4129172</t>
+          <t>3971700; 4121907</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4375691; 4541168</t>
+          <t>4381862; 4542912</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5086372; 5235407</t>
+          <t>5086853; 5234604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3414697; 4081664</t>
+          <t>3965745; 4129626</t>
         </is>
       </c>
     </row>
